--- a/2026年10月_出勤表_平日3組案.xlsx
+++ b/2026年10月_出勤表_平日3組案.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
+          <t>山谷大地</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
           <t>横山凌</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>山谷大地</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -610,9 +610,9 @@
           <t>②</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -622,25 +622,29 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>①</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M3" s="5" t="n"/>
     </row>
     <row r="4">
@@ -655,9 +659,9 @@
       <c r="C4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -677,17 +681,17 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -695,7 +699,11 @@
           <t>③</t>
         </is>
       </c>
-      <c r="L4" s="5" t="n"/>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
       <c r="M4" s="5" t="n"/>
     </row>
     <row r="5">
@@ -730,27 +738,31 @@
           <t>④</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>③</t>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>②</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>④</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="n"/>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
       <c r="M5" s="5" t="n"/>
     </row>
     <row r="6">
@@ -765,9 +777,9 @@
       <c r="C6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>①</t>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -787,25 +799,29 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>④</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>④</t>
+          <t>③</t>
         </is>
       </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="n"/>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
       <c r="M6" s="5" t="n"/>
     </row>
     <row r="7">
@@ -820,14 +836,14 @@
       <c r="C7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -845,9 +861,9 @@
           <t>休</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -857,10 +873,14 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="n"/>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
       <c r="M7" s="5" t="n"/>
     </row>
     <row r="8">
@@ -890,14 +910,14 @@
           <t>休</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -905,17 +925,21 @@
           <t>①</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="n"/>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
       <c r="M8" s="5" t="n"/>
     </row>
     <row r="9">
@@ -945,32 +969,36 @@
           <t>休</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>④</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="n"/>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
       <c r="M9" s="5" t="n"/>
     </row>
     <row r="10">
@@ -990,9 +1018,9 @@
           <t>①</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1000,14 +1028,14 @@
           <t>③</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -1017,15 +1045,19 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="n"/>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M10" s="5" t="n"/>
     </row>
     <row r="11">
@@ -1040,14 +1072,14 @@
       <c r="C11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -1060,19 +1092,19 @@
           <t>④</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1080,7 +1112,11 @@
           <t>③</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
       <c r="M11" s="5" t="n"/>
     </row>
     <row r="12">
@@ -1100,9 +1136,9 @@
           <t>①</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -1117,25 +1153,29 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>④</t>
+          <t>③</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>④</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="n"/>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
       <c r="M12" s="5" t="n"/>
     </row>
     <row r="13">
@@ -1165,32 +1205,36 @@
           <t>③</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>④</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>②</t>
         </is>
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="n"/>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
       <c r="M13" s="5" t="n"/>
     </row>
     <row r="14">
@@ -1215,9 +1259,9 @@
           <t>②</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1225,27 +1269,31 @@
           <t>④</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="n"/>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
       <c r="M14" s="5" t="n"/>
     </row>
     <row r="15">
@@ -1270,9 +1318,9 @@
           <t>②</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1280,27 +1328,31 @@
           <t>④</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>②</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="n"/>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
       <c r="M15" s="5" t="n"/>
     </row>
     <row r="16">
@@ -1320,42 +1372,46 @@
           <t>①</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="n"/>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
       <c r="M16" s="5" t="n"/>
     </row>
     <row r="17">
@@ -1390,9 +1446,9 @@
           <t>休</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1402,15 +1458,19 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="n"/>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M17" s="5" t="n"/>
     </row>
     <row r="18">
@@ -1445,19 +1505,19 @@
           <t>④</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -1465,7 +1525,11 @@
           <t>①</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n"/>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
       <c r="M18" s="5" t="n"/>
     </row>
     <row r="19">
@@ -1490,9 +1554,9 @@
           <t>②</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>③</t>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -1502,12 +1566,12 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>④</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -1517,10 +1581,14 @@
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="n"/>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
       <c r="M19" s="5" t="n"/>
     </row>
     <row r="20">
@@ -1535,9 +1603,9 @@
       <c r="C20" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>①</t>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
@@ -1557,25 +1625,29 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>④</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>②</t>
         </is>
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>④</t>
         </is>
       </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="n"/>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
       <c r="M20" s="5" t="n"/>
     </row>
     <row r="21">
@@ -1590,19 +1662,19 @@
       <c r="C21" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -1612,25 +1684,29 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="n"/>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
       <c r="M21" s="5" t="n"/>
     </row>
     <row r="22">
@@ -1645,14 +1721,14 @@
       <c r="C22" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -1670,9 +1746,9 @@
           <t>休</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1685,7 +1761,11 @@
           <t>④</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n"/>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
       <c r="M22" s="5" t="n"/>
     </row>
     <row r="23">
@@ -1710,37 +1790,41 @@
           <t>②</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="n"/>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
       <c r="M23" s="5" t="n"/>
     </row>
     <row r="24">
@@ -1760,9 +1844,9 @@
           <t>①</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -1777,25 +1861,29 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>①</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="n"/>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M24" s="5" t="n"/>
     </row>
     <row r="25">
@@ -1810,9 +1898,9 @@
       <c r="C25" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -1820,37 +1908,41 @@
           <t>②</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>②</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="n"/>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M25" s="5" t="n"/>
     </row>
     <row r="26">
@@ -1875,9 +1967,9 @@
           <t>②</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>③</t>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
@@ -1887,17 +1979,17 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>④</t>
+          <t>②</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
@@ -1905,7 +1997,11 @@
           <t>①</t>
         </is>
       </c>
-      <c r="L26" s="5" t="n"/>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
       <c r="M26" s="5" t="n"/>
     </row>
     <row r="27">
@@ -1925,9 +2021,9 @@
           <t>①</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
@@ -1942,7 +2038,7 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
@@ -1952,15 +2048,19 @@
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="n"/>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
       <c r="M27" s="5" t="n"/>
     </row>
     <row r="28">
@@ -1975,14 +2075,14 @@
       <c r="C28" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -1990,32 +2090,36 @@
           <t>③</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="n"/>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
       <c r="M28" s="5" t="n"/>
     </row>
     <row r="29">
@@ -2030,9 +2134,9 @@
       <c r="C29" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2045,9 +2149,9 @@
           <t>③</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
@@ -2055,22 +2159,26 @@
           <t>休</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>①</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="n"/>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
       <c r="M29" s="5" t="n"/>
     </row>
     <row r="30">
@@ -2085,9 +2193,9 @@
       <c r="C30" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2095,9 +2203,9 @@
           <t>②</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -2105,27 +2213,31 @@
           <t>④</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="n"/>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
       <c r="M30" s="5" t="n"/>
     </row>
     <row r="31">
@@ -2145,9 +2257,9 @@
           <t>①</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -2162,25 +2274,29 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="J31" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="n"/>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
       <c r="M31" s="5" t="n"/>
     </row>
     <row r="32">
@@ -2200,42 +2316,46 @@
           <t>①</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>①</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="K32" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="n"/>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M32" s="5" t="n"/>
     </row>
     <row r="33">
@@ -2270,19 +2390,19 @@
           <t>④</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>①</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>②</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
@@ -2290,7 +2410,11 @@
           <t>③</t>
         </is>
       </c>
-      <c r="L33" s="5" t="n"/>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
       <c r="M33" s="5" t="n"/>
     </row>
     <row r="34">
@@ -2304,30 +2428,32 @@
         <v>102</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>26</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K34" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="L34" s="5" t="n"/>
+      <c r="L34" s="5" t="n">
+        <v>25</v>
+      </c>
       <c r="M34" s="5" t="n"/>
     </row>
     <row r="35">
@@ -2425,19 +2551,15 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 山谷大地</t>
+          <t>船木智一 ／ 新田</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 新田</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 古川</t>
-        </is>
-      </c>
+          <t>和田陽向太 ／ 古川</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
       <c r="G2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
@@ -2454,11 +2576,7 @@
       <c r="C3" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>船木智一 ／ 古川</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="inlineStr"/>
       <c r="E3" s="5" t="inlineStr"/>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -2467,7 +2585,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 山谷大地</t>
+          <t>山谷大地 ／ 徳留</t>
         </is>
       </c>
     </row>
@@ -2487,22 +2605,22 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 新田</t>
+          <t>船木智一 ／ 山口</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 古川</t>
+          <t>和田陽向太 ／ 新田</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 山谷大地</t>
+          <t>永井海里 ／ 徳留</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 山口</t>
+          <t>山谷大地 ／ 古川</t>
         </is>
       </c>
     </row>
@@ -2520,24 +2638,20 @@
       <c r="C5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>船木智一 ／ 山口</t>
-        </is>
-      </c>
+      <c r="D5" s="5" t="inlineStr"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 山谷大地</t>
+          <t>和田陽向太 ／ 山口</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 新田</t>
+          <t>永井海里 ／ 古川</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 古川</t>
+          <t>山谷大地 ／ 新田</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2669,12 @@
       <c r="C6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 山口</t>
-        </is>
-      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>船木智一 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
           <t>永井海里 ／ 古川</t>
@@ -2568,7 +2682,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 新田</t>
+          <t>山谷大地 ／ 山口</t>
         </is>
       </c>
     </row>
@@ -2593,15 +2707,11 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 山谷大地</t>
+          <t>和田陽向太 ／ 徳留</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>横山凌 ／ 山口</t>
-        </is>
-      </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -2619,20 +2729,16 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 山口</t>
+          <t>船木智一 ／ 古川</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 新田</t>
+          <t>和田陽向太 ／ 徳留</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>横山凌 ／ 山谷大地</t>
-        </is>
-      </c>
+      <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -2650,20 +2756,20 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 山谷大地</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 古川</t>
-        </is>
-      </c>
+          <t>船木智一 ／ 古川</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr">
         <is>
           <t>永井海里 ／ 新田</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>山谷大地 ／ 山口</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -2679,12 +2785,12 @@
       <c r="C10" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>船木智一 ／ 山谷大地</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>和田陽向太 ／ 新田</t>
+        </is>
+      </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
           <t>永井海里 ／ 山口</t>
@@ -2692,7 +2798,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 古川</t>
+          <t>山谷大地 ／ 徳留</t>
         </is>
       </c>
     </row>
@@ -2712,22 +2818,18 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 古川</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 山口</t>
-        </is>
-      </c>
+          <t>船木智一 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 山谷大地</t>
+          <t>永井海里 ／ 新田</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 新田</t>
+          <t>山谷大地 ／ 古川</t>
         </is>
       </c>
     </row>
@@ -2747,24 +2849,20 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 古川</t>
+          <t>船木智一 ／ 山口</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 新田</t>
+          <t>和田陽向太 ／ 古川</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 山口</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>横山凌 ／ 山谷大地</t>
-        </is>
-      </c>
+          <t>永井海里 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -2783,17 +2881,13 @@
       <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 古川</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 新田</t>
-        </is>
-      </c>
+          <t>和田陽向太 ／ 山口</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 山口</t>
+          <t>山谷大地 ／ 徳留</t>
         </is>
       </c>
     </row>
@@ -2814,17 +2908,13 @@
       <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 山口</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 古川</t>
-        </is>
-      </c>
+          <t>和田陽向太 ／ 古川</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 新田</t>
+          <t>山谷大地 ／ 山口</t>
         </is>
       </c>
     </row>
@@ -2844,20 +2934,16 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 山口</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 山谷大地</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>横山凌 ／ 新田</t>
-        </is>
-      </c>
+          <t>船木智一 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>永井海里 ／ 新田</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -2880,12 +2966,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 古川</t>
+          <t>和田陽向太 ／ 山口</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 山谷大地</t>
+          <t>永井海里 ／ 古川</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
@@ -2912,12 +2998,12 @@
       <c r="E17" s="5" t="inlineStr"/>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 山谷大地</t>
+          <t>永井海里 ／ 徳留</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 古川</t>
+          <t>山谷大地 ／ 新田</t>
         </is>
       </c>
     </row>
@@ -2942,17 +3028,13 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 山谷大地</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 新田</t>
-        </is>
-      </c>
+          <t>和田陽向太 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 山口</t>
+          <t>山谷大地 ／ 新田</t>
         </is>
       </c>
     </row>
@@ -2970,24 +3052,20 @@
       <c r="C19" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>船木智一 ／ 新田</t>
-        </is>
-      </c>
+      <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 山口</t>
+          <t>和田陽向太 ／ 新田</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 古川</t>
+          <t>永井海里 ／ 山口</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 山谷大地</t>
+          <t>山谷大地 ／ 古川</t>
         </is>
       </c>
     </row>
@@ -3005,20 +3083,16 @@
       <c r="C20" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>船木智一 ／ 山谷大地</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 山口</t>
-        </is>
-      </c>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>和田陽向太 ／ 山口</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr"/>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 古川</t>
+          <t>山谷大地 ／ 新田</t>
         </is>
       </c>
     </row>
@@ -3036,12 +3110,12 @@
       <c r="C21" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 新田</t>
-        </is>
-      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>船木智一 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
       <c r="F21" s="5" t="inlineStr">
         <is>
           <t>永井海里 ／ 古川</t>
@@ -3049,7 +3123,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 山口</t>
+          <t>山谷大地 ／ 山口</t>
         </is>
       </c>
     </row>
@@ -3069,20 +3143,20 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 新田</t>
+          <t>船木智一 ／ 古川</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 山口</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>横山凌 ／ 山谷大地</t>
-        </is>
-      </c>
+          <t>和田陽向太 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>永井海里 ／ 新田</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -3100,17 +3174,13 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 古川</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 山谷大地</t>
-        </is>
-      </c>
+          <t>船木智一 ／ 新田</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 新田</t>
+          <t>永井海里 ／ 山口</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
@@ -3129,22 +3199,18 @@
       <c r="C24" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>船木智一 ／ 山谷大地</t>
-        </is>
-      </c>
+      <c r="D24" s="5" t="inlineStr"/>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 古川</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 新田</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr"/>
+          <t>和田陽向太 ／ 新田</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>山谷大地 ／ 古川</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -3167,17 +3233,13 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 新田</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 山谷大地</t>
-        </is>
-      </c>
+          <t>和田陽向太 ／ 古川</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr"/>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 古川</t>
+          <t>山谷大地 ／ 徳留</t>
         </is>
       </c>
     </row>
@@ -3197,22 +3259,18 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 山谷大地</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 古川</t>
-        </is>
-      </c>
+          <t>船木智一 ／ 山口</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 山口</t>
+          <t>永井海里 ／ 徳留</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 新田</t>
+          <t>山谷大地 ／ 新田</t>
         </is>
       </c>
     </row>
@@ -3230,22 +3288,18 @@
       <c r="C27" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>船木智一 ／ 山口</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>和田陽向太 ／ 新田</t>
+        </is>
+      </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 山谷大地</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>横山凌 ／ 古川</t>
-        </is>
-      </c>
+          <t>永井海里 ／ 山口</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -3261,22 +3315,22 @@
       <c r="C28" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>船木智一 ／ 古川</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 新田</t>
+          <t>和田陽向太 ／ 山口</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 古川</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>横山凌 ／ 山口</t>
-        </is>
-      </c>
+          <t>永井海里 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -3292,20 +3346,20 @@
       <c r="C29" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>船木智一 ／ 新田</t>
-        </is>
-      </c>
+      <c r="D29" s="5" t="inlineStr"/>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 山口</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr"/>
+          <t>和田陽向太 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>永井海里 ／ 新田</t>
+        </is>
+      </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 山谷大地</t>
+          <t>山谷大地 ／ 古川</t>
         </is>
       </c>
     </row>
@@ -3325,18 +3379,14 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 山口</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 山谷大地</t>
-        </is>
-      </c>
+          <t>船木智一 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 新田</t>
+          <t>山谷大地 ／ 古川</t>
         </is>
       </c>
     </row>
@@ -3356,20 +3406,16 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 古川</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 山谷大地</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 新田</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr"/>
+          <t>船木智一 ／ 新田</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>山谷大地 ／ 山口</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -3387,12 +3433,12 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 古川</t>
+          <t>船木智一 ／ 新田</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 新田</t>
+          <t>和田陽向太 ／ 古川</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -3402,7 +3448,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 山谷大地</t>
+          <t>山谷大地 ／ 徳留</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3483,7 +3529,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>①船木智一、②和田陽向太、③永井海里、④横山凌</t>
+          <t>①船木智一、②和田陽向太、③永井海里、④山谷大地、⑤横山凌</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3541,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>山谷大地、新田、古川、山口</t>
+          <t>新田、古川、山口、徳留</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3567,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>出勤26日／土日9日／公休5日／最大6連勤</t>
+          <t>出勤21日／土日7日／公休10日／最大4連勤</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3579,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>出勤26日／土日9日／公休5日／最大6連勤</t>
+          <t>出勤20日／土日7日／公休11日／最大3連勤</t>
         </is>
       </c>
     </row>
@@ -3545,31 +3591,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>出勤25日／土日9日／公休6日／最大6連勤</t>
+          <t>出勤20日／土日7日／公休11日／最大4連勤</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>横山凌</t>
+          <t>山谷大地</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>出勤25日／土日9日／公休6日／最大6連勤</t>
+          <t>出勤21日／土日8日／公休10日／最大5連勤</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>山谷大地</t>
+          <t>横山凌</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>出勤26日／土日9日／公休5日／最大6連勤</t>
+          <t>出勤20日／土日7日／公休11日／最大5連勤</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3639,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>出勤25日／土日9日／公休6日／最大6連勤</t>
+          <t>出勤26日／土日9日／公休5日／最大6連勤</t>
         </is>
       </c>
     </row>
@@ -3604,6 +3650,18 @@
         </is>
       </c>
       <c r="B19" t="inlineStr">
+        <is>
+          <t>出勤25日／土日9日／公休6日／最大6連勤</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>出勤25日／土日9日／公休6日／最大6連勤</t>
         </is>
